--- a/数值表/QuQu数值表.xlsx
+++ b/数值表/QuQu数值表.xlsx
@@ -16,6 +16,7 @@
     <sheet name="6-状态" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="7-战斗常数" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="8-天赋" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="9-副本难度" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,7 +512,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A19"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -601,44 +602,679 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>9-副本难度   桌面副本的 10 档难度配置</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>注意事项：</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>· 不要改表头名字，不要删列，否则程序读不到</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>· ID 列是程序的索引，改 ID 会导致配置失效</t>
+          <t>· 不要改表头名字，不要删列，否则程序读不到</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>· 想加新属性：先在「1-属性定义」加行，再到「2-品种」加列</t>
+          <t>· ID 列是程序的索引，改 ID 会导致配置失效</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>· 想加新属性：先在「1-属性定义」加行，再到「2-品种」加列</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>· 红底行 = 负面效果；绿底行 = 正面效果</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="11" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>每层敌人数：该难度每一层要连续击败的敌人数量；等级在上下限之间随层数线性提升；品种池填品种ID逗号分隔，「全部」表示所有品种；倍率乘在怪物最终属性上；单杀经验随层数每层+5%；第 20 层为首领层（额外 1.35 倍强度）；解锁前置为需先通关的难度ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>每层敌人数</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>等级下限</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>等级上限</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>品种池</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>HP倍率</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>攻击倍率</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>护甲倍率</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>速度倍率</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>耐力倍率</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>单杀经验</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>层通关经验</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>解锁前置</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>d01</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="inlineStr">
+        <is>
+          <t>新手</t>
+        </is>
+      </c>
+      <c r="C3" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" s="9" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="G3" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H3" s="9" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I3" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J3" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="L3" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="M3" s="9" t="n">
+        <v>33</v>
+      </c>
+      <c r="N3" s="9" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>d02</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>入门</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>13</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I4" s="7" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>d01</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>d03</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>18</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K5" s="6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L5" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="M5" s="6" t="n">
+        <v>78</v>
+      </c>
+      <c r="N5" s="6" t="inlineStr">
+        <is>
+          <t>d02</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>d04</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>初级</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>16</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J6" s="7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K6" s="7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L6" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>111</v>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>d03</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>d05</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>中级</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="K7" s="6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="M7" s="6" t="n">
+        <v>135</v>
+      </c>
+      <c r="N7" s="6" t="inlineStr">
+        <is>
+          <t>d04</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>d06</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>高级</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>28</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>37</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J8" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K8" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L8" s="7" t="n">
+        <v>55</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>165</v>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>d05</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>d07</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>噩梦</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K9" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>231</v>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>d06</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>d08</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>深渊</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>43</v>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="J10" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L10" s="7" t="n">
+        <v>105</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>315</v>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>d07</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>d09</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>绝望</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K11" s="6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L11" s="6" t="n">
+        <v>116</v>
+      </c>
+      <c r="M11" s="6" t="n">
+        <v>348</v>
+      </c>
+      <c r="N11" s="6" t="inlineStr">
+        <is>
+          <t>d08</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>d10</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>真神</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <v>62</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="G12" s="10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I12" s="10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J12" s="10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>142</v>
+      </c>
+      <c r="M12" s="10" t="n">
+        <v>426</v>
+      </c>
+      <c r="N12" s="10" t="inlineStr">
+        <is>
+          <t>d09</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:N1"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1717,7 +2353,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -2557,6 +3193,1306 @@
       </c>
       <c r="H32" s="7" t="n">
         <v>16425</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>1090</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>17515</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="7" t="n">
+        <v>1125</v>
+      </c>
+      <c r="C34" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D34" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F34" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>18640</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>1160</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>19800</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="7" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>1195</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>20995</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>1230</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>22225</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="7" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>1265</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F38" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>23490</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>24790</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>1335</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F40" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>26125</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>27495</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="7" t="n">
+        <v>1405</v>
+      </c>
+      <c r="C42" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="D42" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="G42" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>28900</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>1440</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="6" t="n">
+        <v>30340</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="7" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>1475</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>31815</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>1510</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="6" t="n">
+        <v>33325</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>1545</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>34870</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>1580</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" s="6" t="n">
+        <v>36450</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>1615</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E48" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>38065</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>1650</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" s="6" t="n">
+        <v>39715</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="7" t="n">
+        <v>1685</v>
+      </c>
+      <c r="C50" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D50" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E50" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F50" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="7" t="n">
+        <v>41400</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="6" t="n">
+        <v>1720</v>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D51" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H51" s="6" t="n">
+        <v>43120</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="7" t="n">
+        <v>1755</v>
+      </c>
+      <c r="C52" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D52" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E52" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H52" s="7" t="n">
+        <v>44875</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>1790</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H53" s="6" t="n">
+        <v>46665</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="7" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>1825</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E54" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F54" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>48490</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>1860</v>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D55" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E55" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H55" s="6" t="n">
+        <v>50350</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="7" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>1895</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>52245</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="6" t="n">
+        <v>1930</v>
+      </c>
+      <c r="C57" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D57" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" s="6" t="n">
+        <v>54175</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>1965</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E58" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F58" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>56140</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="6" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C59" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H59" s="6" t="n">
+        <v>58140</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="7" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="7" t="n">
+        <v>2035</v>
+      </c>
+      <c r="C60" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D60" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E60" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" s="7" t="n">
+        <v>60175</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>2070</v>
+      </c>
+      <c r="C61" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D61" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" s="6" t="n">
+        <v>62245</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="7" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="7" t="n">
+        <v>2105</v>
+      </c>
+      <c r="C62" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D62" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E62" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="7" t="n">
+        <v>64350</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="6" t="n">
+        <v>2140</v>
+      </c>
+      <c r="C63" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" s="6" t="n">
+        <v>66490</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="7" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>2175</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>68665</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="6" t="n">
+        <v>2210</v>
+      </c>
+      <c r="C65" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H65" s="6" t="n">
+        <v>70875</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>2245</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E66" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F66" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>73120</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>2280</v>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" s="6" t="n">
+        <v>75400</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="7" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>2315</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E68" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F68" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>77715</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>2350</v>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" s="6" t="n">
+        <v>80065</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="7" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="7" t="n">
+        <v>2385</v>
+      </c>
+      <c r="C70" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H70" s="7" t="n">
+        <v>82450</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="6" t="n">
+        <v>2420</v>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D71" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E71" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H71" s="6" t="n">
+        <v>84870</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" s="7" t="n">
+        <v>2455</v>
+      </c>
+      <c r="C72" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D72" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E72" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F72" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H72" s="7" t="n">
+        <v>87325</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" s="6" t="n">
+        <v>2490</v>
+      </c>
+      <c r="C73" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D73" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E73" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" s="6" t="n">
+        <v>89815</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="7" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>2525</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E74" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F74" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>92340</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>2560</v>
+      </c>
+      <c r="C75" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D75" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E75" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H75" s="6" t="n">
+        <v>94900</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="7" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>2595</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E76" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F76" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>97495</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>2630</v>
+      </c>
+      <c r="C77" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D77" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" s="6" t="n">
+        <v>100125</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="7" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>2665</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E78" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F78" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>102790</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="6" t="n">
+        <v>2700</v>
+      </c>
+      <c r="C79" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D79" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E79" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G79" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H79" s="6" t="n">
+        <v>105490</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="7" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="7" t="n">
+        <v>2735</v>
+      </c>
+      <c r="C80" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D80" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E80" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F80" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G80" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" s="7" t="n">
+        <v>108225</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="6" t="n">
+        <v>2770</v>
+      </c>
+      <c r="C81" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="D81" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E81" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H81" s="6" t="n">
+        <v>110995</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>2805</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E82" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F82" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>113800</v>
       </c>
     </row>
   </sheetData>

--- a/数值表/QuQu数值表.xlsx
+++ b/数值表/QuQu数值表.xlsx
@@ -17,6 +17,9 @@
     <sheet name="7-战斗常数" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="8-天赋" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="9-副本难度" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="10-装备部位" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="11-装备品质" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="12-装备词条" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -512,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -609,38 +612,59 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr"/>
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>10-装备部位   装备槽位定义（可扩展）</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>注意事项：</t>
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>11-装备品质   品质/词条数/数值倍率（可扩展）</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>· 不要改表头名字，不要删列，否则程序读不到</t>
+          <t>12-装备词条   部位×属性的加成词条池（可扩展）</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>· ID 列是程序的索引，改 ID 会导致配置失效</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>· 想加新属性：先在「1-属性定义」加行，再到「2-品种」加列</t>
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>注意事项：</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>· 不要改表头名字，不要删列，否则程序读不到</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>· ID 列是程序的索引，改 ID 会导致配置失效</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>· 想加新属性：先在「1-属性定义」加行，再到「2-品种」加列</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>· 红底行 = 负面效果；绿底行 = 正面效果</t>
         </is>
@@ -657,7 +681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -674,12 +698,14 @@
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="12" customWidth="1" min="13" max="13"/>
     <col width="11" customWidth="1" min="14" max="14"/>
+    <col width="13" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>每层敌人数：该难度每一层要连续击败的敌人数量；等级在上下限之间随层数线性提升；品种池填品种ID逗号分隔，「全部」表示所有品种；倍率乘在怪物最终属性上；单杀经验随层数每层+5%；第 20 层为首领层（额外 1.35 倍强度）；解锁前置为需先通关的难度ID</t>
+          <t>每层敌人数：该难度每一层要连续击败的敌人数量；等级在上下限之间随层数线性提升；品种池填品种ID逗号分隔，「全部」表示所有品种；倍率乘在怪物最终属性上；单杀经验随层数每层+5%；第 20 层为首领层（额外 1.35 倍强度）；解锁前置为需先通关的难度ID；装备掉落概率为击败每个怪物的掉落几率(%)；装备品质权重格式 qID:权重 逗号分隔</t>
         </is>
       </c>
     </row>
@@ -754,6 +780,16 @@
           <t>解锁前置</t>
         </is>
       </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>装备掉落概率</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>装备品质权重</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="inlineStr">
@@ -802,6 +838,14 @@
         <v>33</v>
       </c>
       <c r="N3" s="9" t="inlineStr"/>
+      <c r="O3" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="P3" s="9" t="inlineStr">
+        <is>
+          <t>q01:90,q02:9,q03:1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="inlineStr">
@@ -854,6 +898,14 @@
           <t>d01</t>
         </is>
       </c>
+      <c r="O4" s="7" t="n">
+        <v>24</v>
+      </c>
+      <c r="P4" s="7" t="inlineStr">
+        <is>
+          <t>q01:82,q02:14,q03:4</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -906,6 +958,14 @@
           <t>d02</t>
         </is>
       </c>
+      <c r="O5" s="6" t="n">
+        <v>28</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>q01:74,q02:18,q03:7,q04:1</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="inlineStr">
@@ -958,6 +1018,14 @@
           <t>d03</t>
         </is>
       </c>
+      <c r="O6" s="7" t="n">
+        <v>32</v>
+      </c>
+      <c r="P6" s="7" t="inlineStr">
+        <is>
+          <t>q01:65,q02:21,q03:11,q04:3</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -1010,6 +1078,14 @@
           <t>d04</t>
         </is>
       </c>
+      <c r="O7" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>q01:55,q02:24,q03:15,q04:5,q05:1</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="inlineStr">
@@ -1062,6 +1138,14 @@
           <t>d05</t>
         </is>
       </c>
+      <c r="O8" s="7" t="n">
+        <v>40</v>
+      </c>
+      <c r="P8" s="7" t="inlineStr">
+        <is>
+          <t>q01:45,q02:25,q03:18,q04:8,q05:3,q06:1</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1114,6 +1198,14 @@
           <t>d06</t>
         </is>
       </c>
+      <c r="O9" s="6" t="n">
+        <v>44</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>q01:35,q02:24,q03:21,q04:12,q05:5,q06:2.5,q07:0.5</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
@@ -1166,6 +1258,14 @@
           <t>d07</t>
         </is>
       </c>
+      <c r="O10" s="7" t="n">
+        <v>48</v>
+      </c>
+      <c r="P10" s="7" t="inlineStr">
+        <is>
+          <t>q01:25,q02:22,q03:23,q04:15,q05:9,q06:4.5,q07:1.5</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1218,6 +1318,14 @@
           <t>d08</t>
         </is>
       </c>
+      <c r="O11" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>q01:15,q02:18,q03:24,q04:19,q05:13,q06:8,q07:3</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -1270,10 +1378,1126 @@
           <t>d09</t>
         </is>
       </c>
+      <c r="O12" s="10" t="n">
+        <v>56</v>
+      </c>
+      <c r="P12" s="10" t="inlineStr">
+        <is>
+          <t>q01:8,q02:14,q03:22,q04:22,q05:18,q06:11,q07:5</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>部位可动态扩展：加行即生效。词条倾向仅作设计说明，实际加成由「12-装备词条」的部位列决定</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>词条倾向</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>p01</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>触须</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>速度、耐力回复</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>感知灵敏，久战不疲</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>p02</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>牙齿</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>攻击、暴击</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>牙口决定输出</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>p03</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>前躯</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>血量、护甲</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>躯干护持，能抗能打</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>p04</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>后躯</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>耐力、斗性</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>腰腹爆发，斗志顽强</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>p05</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>翅膀</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>速度、韧性</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>振翅生风，更难被暴击</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>p06</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>尾巴</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>破甲、血量</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>平衡尾舵，撕开防御</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>品质可动态扩展：加行即生效。数值倍率乘在词条基础值上；颜色为 UI 显示色</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>颜色</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>词条数</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>数值倍率</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>q01</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>白色</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>#D5D8DC</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>普通装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>q02</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>夫勇</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>#7DBB6C</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>悍勇装备（绿）</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>q03</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>蓝色</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>#4A90D9</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>铁甲装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>q04</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>紫色</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>#A06BDC</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>纯银装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>q05</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>金色</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>#E8B23A</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>炫金装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>q06</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>橙色</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>#E87A2C</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>无畏装备</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>q07</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>黑金</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>#3A3A45</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>先锋装备（词条按金色列）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>部位可填多个（逗号分隔）或「全部」；属性ID须在「1-属性定义」中登记；最终数值 = 基础值 × 品质数值倍率 × 随机浮动(0.85~1.25)，并有 3% 概率按高 1 档品质生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>ID</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>名称</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>部位</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>属性ID</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>基础值</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>权重</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>描述</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="inlineStr">
+        <is>
+          <t>e01</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>利齿</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>牙齿</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="E3" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="F3" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" s="6" t="inlineStr">
+        <is>
+          <t>咬合更有力，攻击提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>e02</t>
+        </is>
+      </c>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>锋颚</t>
+        </is>
+      </c>
+      <c r="C4" s="8" t="inlineStr">
+        <is>
+          <t>牙齿</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="F4" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>同为大攻词条，数值更高更稀有</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>e03</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>獠牙</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>牙齿</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>55</v>
+      </c>
+      <c r="G5" s="6" t="inlineStr">
+        <is>
+          <t>撕裂防御，破甲提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>e04</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>迅捷触须</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>触须</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>spd</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>反应更快，速度提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>e05</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>灵敏感须</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>触须</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>spd</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="G7" s="6" t="inlineStr">
+        <is>
+          <t>高敏词条，速度大幅提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>e06</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>感知须</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>触须</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>sta_regen</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="G8" s="7" t="inlineStr">
+        <is>
+          <t>感知环境，耐力回复提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>e07</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>坚壳前躯</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>前躯</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>arm</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>外壳硬化，护甲提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>e08</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>厚甲前胸</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>前躯</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="n">
+        <v>30</v>
+      </c>
+      <c r="F10" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>胸甲厚实，血量提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>e09</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>蛮力前肢</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>前躯</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>前肢有力，攻击提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
+        <is>
+          <t>e10</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>爆发后躯</t>
+        </is>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>后躯</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>sta</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="n">
+        <v>20</v>
+      </c>
+      <c r="F12" s="7" t="n">
+        <v>100</v>
+      </c>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>蹬地有力，耐力提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>e11</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>铁腰</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>后躯</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>guts</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>腰杆硬，斗志更顽强</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>e12</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>强健后腿</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
+        <is>
+          <t>后躯</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="n">
+        <v>25</v>
+      </c>
+      <c r="F14" s="7" t="n">
+        <v>70</v>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>后腿粗壮，血量提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>e13</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>轻盈翅膜</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>翅膀</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>spd</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>振翅迅捷，速度提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>e14</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>韧翅</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>翅膀</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>tough</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" s="7" t="n">
+        <v>80</v>
+      </c>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>翅面坚韧，降低被暴击</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>e15</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>鸣音翅</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>翅膀</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>guts</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>鸣声洪亮，斗志提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
+          <t>e16</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>平衡尾</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>尾巴</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>pen</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="F18" s="7" t="n">
+        <v>90</v>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>尾舵稳定发力，破甲提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>e17</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>稳尾</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>尾巴</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>hp</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>80</v>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>尾身扎实，血量提升</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>e18</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>力尾</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>尾巴</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>atk</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="F20" s="7" t="n">
+        <v>50</v>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>甩尾发力，攻击提升</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/数值表/QuQu数值表.xlsx
+++ b/数值表/QuQu数值表.xlsx
@@ -1671,7 +1671,7 @@
       </c>
       <c r="B4" s="7" t="inlineStr">
         <is>
-          <t>夫勇</t>
+          <t>悍勇</t>
         </is>
       </c>
       <c r="C4" s="7" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
-          <t>先锋装备（词条按金色列）</t>
+          <t>先锋装备（深底金纹）</t>
         </is>
       </c>
     </row>
